--- a/src/main/java/com/mycompany/ocxrst/BASES/INVENTARIOS.xlsx
+++ b/src/main/java/com/mycompany/ocxrst/BASES/INVENTARIOS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OCXRST\OrdendeComprasRST\src\main\java\com\mycompany\ocxrst\BASES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3485064A-5636-4398-86DD-7D0F453EC52E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9937B966-F8E3-4C79-8906-B9F33905FA5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{07BBAD01-711C-41B6-957E-FFFDE243DC03}"/>
+    <workbookView xWindow="4800" yWindow="2980" windowWidth="14400" windowHeight="8170" xr2:uid="{07BBAD01-711C-41B6-957E-FFFDE243DC03}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="16">
   <si>
     <t>CODIGO</t>
   </si>
@@ -69,6 +69,21 @@
   </si>
   <si>
     <t>PLUMON</t>
+  </si>
+  <si>
+    <t>PLUM4</t>
+  </si>
+  <si>
+    <t>L4P1Z</t>
+  </si>
+  <si>
+    <t>S4C4PUNT4</t>
+  </si>
+  <si>
+    <t>GOM4</t>
+  </si>
+  <si>
+    <t>T3CL4DO</t>
   </si>
 </sst>
 </file>
@@ -466,8 +481,8 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="1">
-        <v>1</v>
+      <c r="A2" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -480,8 +495,8 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="1">
-        <v>2</v>
+      <c r="A3" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
@@ -494,8 +509,8 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="1">
-        <v>3</v>
+      <c r="A4" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>8</v>
@@ -508,8 +523,8 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="1">
-        <v>4</v>
+      <c r="A5" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>6</v>
@@ -522,8 +537,8 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="1">
-        <v>5</v>
+      <c r="A6" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
@@ -536,8 +551,8 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="1">
-        <v>6</v>
+      <c r="A7" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>10</v>

--- a/src/main/java/com/mycompany/ocxrst/BASES/INVENTARIOS.xlsx
+++ b/src/main/java/com/mycompany/ocxrst/BASES/INVENTARIOS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OCXRST\OrdendeComprasRST\src\main\java\com\mycompany\ocxrst\BASES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9937B966-F8E3-4C79-8906-B9F33905FA5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{156E3ABC-3A4B-41D7-B90B-DA0F5805BFDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4800" yWindow="2980" windowWidth="14400" windowHeight="8170" xr2:uid="{07BBAD01-711C-41B6-957E-FFFDE243DC03}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{07BBAD01-711C-41B6-957E-FFFDE243DC03}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>

--- a/src/main/java/com/mycompany/ocxrst/BASES/INVENTARIOS.xlsx
+++ b/src/main/java/com/mycompany/ocxrst/BASES/INVENTARIOS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OCXRST\OrdendeComprasRST\src\main\java\com\mycompany\ocxrst\BASES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{156E3ABC-3A4B-41D7-B90B-DA0F5805BFDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5115568C-591C-4DCC-A2C7-5FE1CC6E18B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{07BBAD01-711C-41B6-957E-FFFDE243DC03}"/>
+    <workbookView xWindow="3330" yWindow="2290" windowWidth="14400" windowHeight="8170" xr2:uid="{07BBAD01-711C-41B6-957E-FFFDE243DC03}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
   <si>
     <t>CODIGO</t>
   </si>
@@ -53,37 +53,28 @@
     <t>PZS</t>
   </si>
   <si>
-    <t>LAPIZ</t>
-  </si>
-  <si>
-    <t>GOMA</t>
-  </si>
-  <si>
-    <t>PLUMA</t>
-  </si>
-  <si>
-    <t>SACAPUNTA</t>
-  </si>
-  <si>
-    <t>TECLADO</t>
-  </si>
-  <si>
-    <t>PLUMON</t>
-  </si>
-  <si>
-    <t>PLUM4</t>
-  </si>
-  <si>
-    <t>L4P1Z</t>
-  </si>
-  <si>
-    <t>S4C4PUNT4</t>
-  </si>
-  <si>
-    <t>GOM4</t>
-  </si>
-  <si>
-    <t>T3CL4DO</t>
+    <t>W2300A</t>
+  </si>
+  <si>
+    <t>W2301A</t>
+  </si>
+  <si>
+    <t>W2302A</t>
+  </si>
+  <si>
+    <t>W2303A</t>
+  </si>
+  <si>
+    <t>Tóner original W2300A Negro</t>
+  </si>
+  <si>
+    <t>Tóner original W2300A Cian</t>
+  </si>
+  <si>
+    <t>Tóner original W2300A Amarillo</t>
+  </si>
+  <si>
+    <t>Tóner original W2300A Magenta</t>
   </si>
 </sst>
 </file>
@@ -119,9 +110,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -458,10 +452,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{877AF9B0-D8EB-40CB-AC5E-6B8E2D94635F}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.90625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
   </cols>
@@ -482,86 +476,58 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="1">
-        <v>12</v>
+      <c r="D2" s="2">
+        <v>1771.62</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="1">
-        <v>8</v>
+      <c r="D3" s="2">
+        <v>2137.5100000000002</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="1">
-        <v>6</v>
+      <c r="D4" s="2">
+        <v>2137.5100000000002</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" s="1">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="1">
-        <v>25</v>
+      <c r="D5" s="2">
+        <v>2137.5100000000002</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/java/com/mycompany/ocxrst/BASES/INVENTARIOS.xlsx
+++ b/src/main/java/com/mycompany/ocxrst/BASES/INVENTARIOS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OCXRST\OrdendeComprasRST\src\main\java\com\mycompany\ocxrst\BASES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5115568C-591C-4DCC-A2C7-5FE1CC6E18B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3460423-5395-4E57-A01B-0D179C3CFCEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3330" yWindow="2290" windowWidth="14400" windowHeight="8170" xr2:uid="{07BBAD01-711C-41B6-957E-FFFDE243DC03}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{07BBAD01-711C-41B6-957E-FFFDE243DC03}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
   <si>
     <t>CODIGO</t>
   </si>
@@ -50,9 +50,6 @@
     <t>PRECIOUNITARIO</t>
   </si>
   <si>
-    <t>PZS</t>
-  </si>
-  <si>
     <t>W2300A</t>
   </si>
   <si>
@@ -75,6 +72,12 @@
   </si>
   <si>
     <t>Tóner original W2300A Magenta</t>
+  </si>
+  <si>
+    <t>PZA</t>
+  </si>
+  <si>
+    <t>CANTIDAD</t>
   </si>
 </sst>
 </file>
@@ -452,15 +455,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{877AF9B0-D8EB-40CB-AC5E-6B8E2D94635F}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="25.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.1796875" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -473,61 +476,76 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D2" s="2">
         <v>1771.62</v>
       </c>
+      <c r="E2">
+        <v>10</v>
+      </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D3" s="2">
         <v>2137.5100000000002</v>
       </c>
+      <c r="E3">
+        <v>10</v>
+      </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D4" s="2">
         <v>2137.5100000000002</v>
       </c>
+      <c r="E4">
+        <v>10</v>
+      </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="D5" s="2">
         <v>2137.5100000000002</v>
+      </c>
+      <c r="E5">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/java/com/mycompany/ocxrst/BASES/INVENTARIOS.xlsx
+++ b/src/main/java/com/mycompany/ocxrst/BASES/INVENTARIOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OCXRST\OrdendeComprasRST\src\main\java\com\mycompany\ocxrst\BASES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3460423-5395-4E57-A01B-0D179C3CFCEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99CA9354-6373-466A-A97B-C4C867EFC508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{07BBAD01-711C-41B6-957E-FFFDE243DC03}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="50">
   <si>
     <t>CODIGO</t>
   </si>
@@ -78,6 +78,114 @@
   </si>
   <si>
     <t>CANTIDAD</t>
+  </si>
+  <si>
+    <t>HP1020</t>
+  </si>
+  <si>
+    <t>Papel bond tamaño carta 75g</t>
+  </si>
+  <si>
+    <t>PAQ</t>
+  </si>
+  <si>
+    <t>HP1021</t>
+  </si>
+  <si>
+    <t>Papel bond tamaño oficio 75g</t>
+  </si>
+  <si>
+    <t>CAN001</t>
+  </si>
+  <si>
+    <t>Cartucho Canon CL-211 Color</t>
+  </si>
+  <si>
+    <t>CAN002</t>
+  </si>
+  <si>
+    <t>Cartucho Canon PG-210 Negro</t>
+  </si>
+  <si>
+    <t>EPSON01</t>
+  </si>
+  <si>
+    <t>Tinta Epson 544 Negro</t>
+  </si>
+  <si>
+    <t>ML</t>
+  </si>
+  <si>
+    <t>EPSON02</t>
+  </si>
+  <si>
+    <t>Tinta Epson 544 Cian</t>
+  </si>
+  <si>
+    <t>EPSON03</t>
+  </si>
+  <si>
+    <t>Tinta Epson 544 Magenta</t>
+  </si>
+  <si>
+    <t>EPSON04</t>
+  </si>
+  <si>
+    <t>Tinta Epson 544 Amarillo</t>
+  </si>
+  <si>
+    <t>USB001</t>
+  </si>
+  <si>
+    <t>Memoria USB 32GB Kingston</t>
+  </si>
+  <si>
+    <t>USB002</t>
+  </si>
+  <si>
+    <t>Memoria USB 64GB Kingston</t>
+  </si>
+  <si>
+    <t>DISC01</t>
+  </si>
+  <si>
+    <t>Disco duro externo 1TB Seagate</t>
+  </si>
+  <si>
+    <t>MOUSE01</t>
+  </si>
+  <si>
+    <t>Mouse óptico inalámbrico Logitech</t>
+  </si>
+  <si>
+    <t>KEYB01</t>
+  </si>
+  <si>
+    <t>Teclado USB estándar Logitech</t>
+  </si>
+  <si>
+    <t>MONI01</t>
+  </si>
+  <si>
+    <t>Monitor LED 21.5 pulgadas HP</t>
+  </si>
+  <si>
+    <t>LAPB01</t>
+  </si>
+  <si>
+    <t>Base para laptop con ventilador</t>
+  </si>
+  <si>
+    <t>CABL01</t>
+  </si>
+  <si>
+    <t>Cable HDMI 2 metros</t>
+  </si>
+  <si>
+    <t>REGU01</t>
+  </si>
+  <si>
+    <t>Regulador de voltaje 1000VA</t>
   </si>
 </sst>
 </file>
@@ -116,10 +224,10 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -455,12 +563,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{877AF9B0-D8EB-40CB-AC5E-6B8E2D94635F}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="36.1796875" customWidth="1"/>
-    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.90625" style="1"/>
+    <col min="2" max="2" width="36.1796875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.90625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
@@ -493,7 +603,7 @@
       <c r="D2" s="2">
         <v>1771.62</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <v>10</v>
       </c>
     </row>
@@ -510,7 +620,7 @@
       <c r="D3" s="2">
         <v>2137.5100000000002</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <v>10</v>
       </c>
     </row>
@@ -527,7 +637,7 @@
       <c r="D4" s="2">
         <v>2137.5100000000002</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <v>10</v>
       </c>
     </row>
@@ -544,8 +654,297 @@
       <c r="D5" s="2">
         <v>2137.5100000000002</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="1">
+        <v>95.5</v>
+      </c>
+      <c r="E6" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="1">
+        <v>110.25</v>
+      </c>
+      <c r="E7" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="1">
+        <v>620</v>
+      </c>
+      <c r="E8" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="1">
+        <v>580</v>
+      </c>
+      <c r="E9" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="1">
+        <v>210.75</v>
+      </c>
+      <c r="E10" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="1">
+        <v>205.6</v>
+      </c>
+      <c r="E11" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="1">
+        <v>205.6</v>
+      </c>
+      <c r="E12" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="1">
+        <v>205.6</v>
+      </c>
+      <c r="E13" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="1">
+        <v>120</v>
+      </c>
+      <c r="E14" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="1">
+        <v>180</v>
+      </c>
+      <c r="E15" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="2">
+        <v>1250</v>
+      </c>
+      <c r="E16" s="1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="1">
+        <v>220</v>
+      </c>
+      <c r="E17" s="1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="1">
+        <v>310</v>
+      </c>
+      <c r="E18" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="2">
+        <v>2850</v>
+      </c>
+      <c r="E19" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" s="1">
+        <v>450</v>
+      </c>
+      <c r="E20" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="1">
+        <v>95</v>
+      </c>
+      <c r="E21" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" s="1">
+        <v>780</v>
+      </c>
+      <c r="E22" s="1">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/java/com/mycompany/ocxrst/BASES/INVENTARIOS.xlsx
+++ b/src/main/java/com/mycompany/ocxrst/BASES/INVENTARIOS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OCXRST\OrdendeComprasRST\src\main\java\com\mycompany\ocxrst\BASES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99CA9354-6373-466A-A97B-C4C867EFC508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC3B2A8D-0A2D-4F85-9250-B785CC0B40A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{07BBAD01-711C-41B6-957E-FFFDE243DC03}"/>
+    <workbookView xWindow="3110" yWindow="200" windowWidth="14400" windowHeight="8170" xr2:uid="{07BBAD01-711C-41B6-957E-FFFDE243DC03}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="51">
   <si>
     <t>CODIGO</t>
   </si>
@@ -44,12 +44,6 @@
     <t>DESCRIPCION</t>
   </si>
   <si>
-    <t>UNIDADMEDIDA</t>
-  </si>
-  <si>
-    <t>PRECIOUNITARIO</t>
-  </si>
-  <si>
     <t>W2300A</t>
   </si>
   <si>
@@ -186,6 +180,15 @@
   </si>
   <si>
     <t>Regulador de voltaje 1000VA</t>
+  </si>
+  <si>
+    <t>ACTIVO</t>
+  </si>
+  <si>
+    <t>UNIDAD</t>
+  </si>
+  <si>
+    <t>PRECIO_UNITARIO</t>
   </si>
 </sst>
 </file>
@@ -221,12 +224,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -563,17 +569,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{877AF9B0-D8EB-40CB-AC5E-6B8E2D94635F}">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.90625" style="1"/>
-    <col min="2" max="2" width="36.1796875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.90625" style="1"/>
+    <col min="1" max="1" width="10.90625" style="1" collapsed="1"/>
+    <col min="2" max="2" width="36.1796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="14" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="15" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="10.90625" style="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -581,41 +587,47 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2">
         <v>1771.62</v>
       </c>
-      <c r="E2" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E2" s="3">
+        <v>40</v>
+      </c>
+      <c r="F2" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2">
         <v>2137.5100000000002</v>
@@ -623,16 +635,19 @@
       <c r="E3" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F3" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2">
         <v>2137.5100000000002</v>
@@ -640,16 +655,19 @@
       <c r="E4" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F4" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D5" s="2">
         <v>2137.5100000000002</v>
@@ -657,16 +675,19 @@
       <c r="E5" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>16</v>
       </c>
       <c r="D6" s="1">
         <v>95.5</v>
@@ -674,16 +695,19 @@
       <c r="E6" s="1">
         <v>50</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D7" s="1">
         <v>110.25</v>
@@ -691,16 +715,19 @@
       <c r="E7" s="1">
         <v>40</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D8" s="1">
         <v>620</v>
@@ -708,16 +735,19 @@
       <c r="E8" s="1">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F8" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D9" s="1">
         <v>580</v>
@@ -725,16 +755,19 @@
       <c r="E9" s="1">
         <v>18</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F9" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="D10" s="1">
         <v>210.75</v>
@@ -742,16 +775,19 @@
       <c r="E10" s="1">
         <v>25</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F10" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D11" s="1">
         <v>205.6</v>
@@ -759,16 +795,19 @@
       <c r="E11" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D12" s="1">
         <v>205.6</v>
@@ -776,16 +815,19 @@
       <c r="E12" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F12" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D13" s="1">
         <v>205.6</v>
@@ -793,16 +835,19 @@
       <c r="E13" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D14" s="1">
         <v>120</v>
@@ -810,16 +855,19 @@
       <c r="E14" s="1">
         <v>30</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F14" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D15" s="1">
         <v>180</v>
@@ -827,16 +875,19 @@
       <c r="E15" s="1">
         <v>25</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F15" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D16" s="2">
         <v>1250</v>
@@ -844,16 +895,19 @@
       <c r="E16" s="1">
         <v>12</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F16" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D17" s="1">
         <v>220</v>
@@ -861,16 +915,19 @@
       <c r="E17" s="1">
         <v>35</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F17" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D18" s="1">
         <v>310</v>
@@ -878,16 +935,19 @@
       <c r="E18" s="1">
         <v>28</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F18" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D19" s="2">
         <v>2850</v>
@@ -895,16 +955,19 @@
       <c r="E19" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F19" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D20" s="1">
         <v>450</v>
@@ -912,16 +975,19 @@
       <c r="E20" s="1">
         <v>22</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F20" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D21" s="1">
         <v>95</v>
@@ -929,22 +995,28 @@
       <c r="E21" s="1">
         <v>60</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F21" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D22" s="1">
         <v>780</v>
       </c>
       <c r="E22" s="1">
         <v>14</v>
+      </c>
+      <c r="F22" s="1">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
